--- a/KatalonData/RADTestData/MFLNNotZero.xlsx
+++ b/KatalonData/RADTestData/MFLNNotZero.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>Result</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>Thu Jul 09 23:02:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:45:23 IST 2026</t>
+  </si>
+  <si>
+    <t>Sat Aug 15 02:45:51 IST 2026</t>
   </si>
 </sst>
 </file>
@@ -497,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -514,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>

--- a/KatalonData/RADTestData/MFLNNotZero.xlsx
+++ b/KatalonData/RADTestData/MFLNNotZero.xlsx
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="16">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="18">
   <si>
     <t>Result</t>
   </si>
@@ -87,6 +87,12 @@
   </si>
   <si>
     <t>Thu Jul 09 23:02:23 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:17:29 EDT 2026</t>
+  </si>
+  <si>
+    <t>Thu Sep 03 22:17:41 EDT 2026</t>
   </si>
 </sst>
 </file>
@@ -497,7 +503,7 @@
         <v>9</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="C2" s="1" t="s">
         <v>6</v>
@@ -514,7 +520,7 @@
         <v>9</v>
       </c>
       <c r="B3" s="1" t="s">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="C3" s="1" t="s">
         <v>6</v>
